--- a/overview.xlsx
+++ b/overview.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vinmas/repositories/os_material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98192B15-0A4C-594F-9D18-ACFAD5D5BF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1222419-DE57-3349-B4A2-B90B4206F08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="660" windowWidth="28040" windowHeight="17020" xr2:uid="{67D7C5C9-BFD9-9043-B236-4D7F530C133A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="114">
   <si>
     <t>Lecture</t>
   </si>
@@ -375,13 +375,19 @@
   </si>
   <si>
     <t>Would be nice to add slides/video on different sile systems too (FAT…)</t>
+  </si>
+  <si>
+    <t>If we are no longer pointing to Silberschatz, those instructions should go from the slides</t>
+  </si>
+  <si>
+    <t>should check cutting in the beginning If we are no longer pointing to Silberschatz, those instructions should go from the slides</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -391,6 +397,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -422,11 +435,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -935,6 +949,9 @@
       <c r="H6" t="s">
         <v>14</v>
       </c>
+      <c r="I6" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -1117,6 +1134,9 @@
       <c r="H13" t="s">
         <v>14</v>
       </c>
+      <c r="I13" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1196,7 +1216,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1222,7 +1242,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1248,7 +1268,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
@@ -1274,7 +1294,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>12</v>
       </c>
@@ -1300,7 +1320,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
@@ -1325,8 +1345,11 @@
       <c r="H21" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>13</v>
       </c>
@@ -1352,7 +1375,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
@@ -1378,7 +1401,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -1404,7 +1427,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
@@ -1430,7 +1453,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
@@ -1456,7 +1479,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>13</v>
       </c>
@@ -1482,7 +1505,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>20</v>
       </c>
@@ -1507,8 +1530,11 @@
       <c r="H28" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>20</v>
       </c>
@@ -1534,7 +1560,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>20</v>
       </c>
@@ -1560,7 +1586,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>20</v>
       </c>
@@ -1586,7 +1612,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>20</v>
       </c>
@@ -1690,6 +1716,9 @@
       <c r="H35" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="I35" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -1928,7 +1957,7 @@
         <v>14</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
@@ -2128,6 +2157,9 @@
       <c r="H51" t="s">
         <v>14</v>
       </c>
+      <c r="I51" s="4" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
@@ -2311,6 +2343,9 @@
       <c r="H58" t="s">
         <v>14</v>
       </c>
+      <c r="I58" s="4" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
@@ -2497,6 +2532,9 @@
       <c r="H65" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="I65" s="4" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
@@ -2654,6 +2692,9 @@
       <c r="H71" t="s">
         <v>14</v>
       </c>
+      <c r="I71" s="4" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
@@ -2862,6 +2903,9 @@
       </c>
       <c r="H79" t="s">
         <v>14</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
